--- a/Ecuatia de Stare/izobara.xlsx
+++ b/Ecuatia de Stare/izobara.xlsx
@@ -268,7 +268,7 @@
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.21"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.22"/>
   </cols>
@@ -294,21 +294,10 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>0</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
       <c r="H2" s="1" t="n">
         <f aca="false">D3/1000000</f>
         <v>5.9E-005</v>
